--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132359657</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132359052</v>
+        <v>132344678</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,31 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509089</v>
+        <v>509037</v>
       </c>
       <c r="R3" t="n">
-        <v>6716171</v>
+        <v>6716102</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,7 +854,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>17 fk små.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,28 +863,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132344678</v>
+        <v>132359052</v>
       </c>
       <c r="B4" t="n">
-        <v>92188</v>
+        <v>57948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,26 +893,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -924,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509037</v>
+        <v>509089</v>
       </c>
       <c r="R4" t="n">
-        <v>6716102</v>
+        <v>6716171</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>17 fk små.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,19 +974,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -995,7 +995,7 @@
         <v>132359213</v>
       </c>
       <c r="B5" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>132344679</v>
       </c>
       <c r="B6" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>132344675</v>
       </c>
       <c r="B8" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>132359304</v>
       </c>
       <c r="B9" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>132359353</v>
       </c>
       <c r="B10" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>132344677</v>
       </c>
       <c r="B11" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>132344676</v>
       </c>
       <c r="B12" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>132359450</v>
       </c>
       <c r="B13" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>132344674</v>
       </c>
       <c r="B14" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>132344681</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>132359137</v>
       </c>
       <c r="B16" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>132359184</v>
       </c>
       <c r="B17" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>132359418</v>
       </c>
       <c r="B18" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>132359393</v>
       </c>
       <c r="B19" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132359259</v>
+        <v>132359149</v>
       </c>
       <c r="B20" t="n">
-        <v>92188</v>
+        <v>91892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509095</v>
+        <v>509082</v>
       </c>
       <c r="R20" t="n">
-        <v>6716085</v>
+        <v>6716062</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132359149</v>
+        <v>132359259</v>
       </c>
       <c r="B21" t="n">
-        <v>91889</v>
+        <v>92191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509082</v>
+        <v>509095</v>
       </c>
       <c r="R21" t="n">
-        <v>6716062</v>
+        <v>6716085</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>132359333</v>
       </c>
       <c r="B22" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -2542,10 +2542,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132359149</v>
+        <v>132359259</v>
       </c>
       <c r="B20" t="n">
-        <v>91892</v>
+        <v>92191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509082</v>
+        <v>509095</v>
       </c>
       <c r="R20" t="n">
-        <v>6716062</v>
+        <v>6716085</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132359259</v>
+        <v>132359149</v>
       </c>
       <c r="B21" t="n">
-        <v>92191</v>
+        <v>91892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509095</v>
+        <v>509082</v>
       </c>
       <c r="R21" t="n">
-        <v>6716085</v>
+        <v>6716062</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132359657</v>
+        <v>132359052</v>
       </c>
       <c r="B2" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509226</v>
+        <v>509089</v>
       </c>
       <c r="R2" t="n">
-        <v>6716352</v>
+        <v>6716171</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,13 +756,17 @@
           <t>2026-04-10</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -882,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132359052</v>
+        <v>132359657</v>
       </c>
       <c r="B4" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,31 +902,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509089</v>
+        <v>509226</v>
       </c>
       <c r="R4" t="n">
-        <v>6716171</v>
+        <v>6716352</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -963,17 +967,13 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132359137</v>
+        <v>132359184</v>
       </c>
       <c r="B16" t="n">
         <v>91892</v>
@@ -2176,13 +2176,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509088</v>
+        <v>509103</v>
       </c>
       <c r="R16" t="n">
-        <v>6716080</v>
+        <v>6716073</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132359184</v>
+        <v>132359137</v>
       </c>
       <c r="B17" t="n">
         <v>91892</v>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509103</v>
+        <v>509088</v>
       </c>
       <c r="R17" t="n">
-        <v>6716073</v>
+        <v>6716080</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132359052</v>
+        <v>132344678</v>
       </c>
       <c r="B2" t="n">
-        <v>57948</v>
+        <v>92197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509089</v>
+        <v>509037</v>
       </c>
       <c r="R2" t="n">
-        <v>6716171</v>
+        <v>6716102</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>17 fk små.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132344678</v>
+        <v>132359657</v>
       </c>
       <c r="B3" t="n">
-        <v>92191</v>
+        <v>91898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509037</v>
+        <v>509226</v>
       </c>
       <c r="R3" t="n">
-        <v>6716102</v>
+        <v>6716352</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,11 +855,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>17 fk små.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,22 +870,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132359657</v>
+        <v>132359052</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,26 +893,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509226</v>
+        <v>509089</v>
       </c>
       <c r="R4" t="n">
-        <v>6716352</v>
+        <v>6716171</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -967,13 +963,17 @@
           <t>2026-04-10</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,7 +995,7 @@
         <v>132359213</v>
       </c>
       <c r="B5" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>132344679</v>
       </c>
       <c r="B6" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>132359089</v>
       </c>
       <c r="B7" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>132344675</v>
       </c>
       <c r="B8" t="n">
-        <v>92615</v>
+        <v>92621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>132359304</v>
       </c>
       <c r="B9" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>132359353</v>
       </c>
       <c r="B10" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>132344677</v>
       </c>
       <c r="B11" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>132344676</v>
       </c>
       <c r="B12" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>132359450</v>
       </c>
       <c r="B13" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>132344674</v>
       </c>
       <c r="B14" t="n">
-        <v>92615</v>
+        <v>92621</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>132344681</v>
       </c>
       <c r="B15" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132359184</v>
+        <v>132359137</v>
       </c>
       <c r="B16" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,13 +2176,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509103</v>
+        <v>509088</v>
       </c>
       <c r="R16" t="n">
-        <v>6716073</v>
+        <v>6716080</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132359137</v>
+        <v>132359184</v>
       </c>
       <c r="B17" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509088</v>
+        <v>509103</v>
       </c>
       <c r="R17" t="n">
-        <v>6716080</v>
+        <v>6716073</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>132359418</v>
       </c>
       <c r="B18" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>132359393</v>
       </c>
       <c r="B19" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>132359259</v>
       </c>
       <c r="B20" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>132359149</v>
       </c>
       <c r="B21" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>132359333</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132344678</v>
       </c>
       <c r="B2" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132359657</v>
       </c>
       <c r="B3" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>132359052</v>
       </c>
       <c r="B4" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>132359213</v>
       </c>
       <c r="B5" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>132344679</v>
       </c>
       <c r="B6" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>132359089</v>
       </c>
       <c r="B7" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>132344675</v>
       </c>
       <c r="B8" t="n">
-        <v>92621</v>
+        <v>92631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>132359304</v>
       </c>
       <c r="B9" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>132359353</v>
       </c>
       <c r="B10" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>132344677</v>
       </c>
       <c r="B11" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>132344676</v>
       </c>
       <c r="B12" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>132359450</v>
       </c>
       <c r="B13" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>132344674</v>
       </c>
       <c r="B14" t="n">
-        <v>92621</v>
+        <v>92631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>132344681</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>132359137</v>
       </c>
       <c r="B16" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>132359184</v>
       </c>
       <c r="B17" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>132359418</v>
       </c>
       <c r="B18" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>132359393</v>
       </c>
       <c r="B19" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>132359259</v>
       </c>
       <c r="B20" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>132359149</v>
       </c>
       <c r="B21" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>132359333</v>
       </c>
       <c r="B22" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132344678</v>
       </c>
       <c r="B2" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132359657</v>
       </c>
       <c r="B3" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>132359213</v>
       </c>
       <c r="B5" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>132344679</v>
       </c>
       <c r="B6" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>132344675</v>
       </c>
       <c r="B8" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>132359304</v>
       </c>
       <c r="B9" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>132359353</v>
       </c>
       <c r="B10" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>132344677</v>
       </c>
       <c r="B11" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>132344676</v>
       </c>
       <c r="B12" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>132359450</v>
       </c>
       <c r="B13" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>132344674</v>
       </c>
       <c r="B14" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>132344681</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>132359137</v>
       </c>
       <c r="B16" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132359184</v>
+        <v>132359418</v>
       </c>
       <c r="B17" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509103</v>
+        <v>509155</v>
       </c>
       <c r="R17" t="n">
-        <v>6716073</v>
+        <v>6716231</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132359418</v>
+        <v>132359184</v>
       </c>
       <c r="B18" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,13 +2378,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509155</v>
+        <v>509103</v>
       </c>
       <c r="R18" t="n">
-        <v>6716231</v>
+        <v>6716073</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>132359393</v>
       </c>
       <c r="B19" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>132359259</v>
       </c>
       <c r="B20" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>132359149</v>
       </c>
       <c r="B21" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>132359333</v>
       </c>
       <c r="B22" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132344678</v>
+        <v>132359052</v>
       </c>
       <c r="B2" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509037</v>
+        <v>509089</v>
       </c>
       <c r="R2" t="n">
-        <v>6716102</v>
+        <v>6716171</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>17 fk små.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,19 +767,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -882,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132359052</v>
+        <v>132344678</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,31 +897,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509089</v>
+        <v>509037</v>
       </c>
       <c r="R4" t="n">
-        <v>6716171</v>
+        <v>6716102</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>17 fk små.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,18 +973,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132359418</v>
+        <v>132359184</v>
       </c>
       <c r="B17" t="n">
         <v>91909</v>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509155</v>
+        <v>509103</v>
       </c>
       <c r="R17" t="n">
-        <v>6716231</v>
+        <v>6716073</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132359184</v>
+        <v>132359418</v>
       </c>
       <c r="B18" t="n">
         <v>91909</v>
@@ -2378,13 +2378,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509103</v>
+        <v>509155</v>
       </c>
       <c r="R18" t="n">
-        <v>6716073</v>
+        <v>6716231</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132359052</v>
+        <v>132359657</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509089</v>
+        <v>509226</v>
       </c>
       <c r="R2" t="n">
-        <v>6716171</v>
+        <v>6716352</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +751,13 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132359657</v>
+        <v>132359052</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,26 +787,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509226</v>
+        <v>509089</v>
       </c>
       <c r="R3" t="n">
-        <v>6716352</v>
+        <v>6716171</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,13 +857,17 @@
           <t>2026-04-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132344678</v>
+        <v>132344677</v>
       </c>
       <c r="B2" t="n">
-        <v>92215</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509037</v>
+        <v>509040</v>
       </c>
       <c r="R2" t="n">
-        <v>6716102</v>
+        <v>6716077</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>17 fk små.</t>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132359657</v>
+        <v>132344678</v>
       </c>
       <c r="B3" t="n">
-        <v>91916</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509226</v>
+        <v>509037</v>
       </c>
       <c r="R3" t="n">
-        <v>6716352</v>
+        <v>6716102</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,6 +855,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>17 fk små.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132359052</v>
+        <v>132344679</v>
       </c>
       <c r="B4" t="n">
-        <v>57957</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,31 +898,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509089</v>
+        <v>509028</v>
       </c>
       <c r="R4" t="n">
-        <v>6716171</v>
+        <v>6716118</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>8 fk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,28 +974,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132359213</v>
+        <v>132359259</v>
       </c>
       <c r="B5" t="n">
-        <v>91916</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509071</v>
+        <v>509095</v>
       </c>
       <c r="R5" t="n">
-        <v>6716089</v>
+        <v>6716085</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132344679</v>
+        <v>132359304</v>
       </c>
       <c r="B6" t="n">
-        <v>92215</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,7 +1122,11 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1131,13 +1136,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509028</v>
+        <v>509060</v>
       </c>
       <c r="R6" t="n">
-        <v>6716118</v>
+        <v>6716209</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1167,11 +1172,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>8 fk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,22 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132359089</v>
+        <v>132359353</v>
       </c>
       <c r="B7" t="n">
-        <v>57957</v>
+        <v>92245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,31 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509102</v>
+        <v>509149</v>
       </c>
       <c r="R7" t="n">
-        <v>6716083</v>
+        <v>6716226</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,17 +1283,13 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1309,36 +1308,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132344675</v>
+        <v>132359450</v>
       </c>
       <c r="B8" t="n">
-        <v>92639</v>
+        <v>92245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1347,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509242</v>
+        <v>509180</v>
       </c>
       <c r="R8" t="n">
-        <v>6716353</v>
+        <v>6716322</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,22 +1405,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132359304</v>
+        <v>132359137</v>
       </c>
       <c r="B9" t="n">
-        <v>92215</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,28 +1428,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1452,13 +1455,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509060</v>
+        <v>509088</v>
       </c>
       <c r="R9" t="n">
-        <v>6716209</v>
+        <v>6716080</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1515,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132359353</v>
+        <v>132359149</v>
       </c>
       <c r="B10" t="n">
-        <v>92215</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,33 +1529,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509149</v>
+        <v>509082</v>
       </c>
       <c r="R10" t="n">
-        <v>6716226</v>
+        <v>6716062</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132344677</v>
+        <v>132359184</v>
       </c>
       <c r="B11" t="n">
-        <v>92215</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,13 +1657,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509040</v>
+        <v>509103</v>
       </c>
       <c r="R11" t="n">
-        <v>6716077</v>
+        <v>6716073</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1698,11 +1693,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1 fk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,44 +1708,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132344676</v>
+        <v>132359213</v>
       </c>
       <c r="B12" t="n">
-        <v>92376</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,13 +1758,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509232</v>
+        <v>509071</v>
       </c>
       <c r="R12" t="n">
-        <v>6716372</v>
+        <v>6716089</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1819,22 +1809,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132359450</v>
+        <v>132359333</v>
       </c>
       <c r="B13" t="n">
-        <v>92215</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,33 +1832,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1877,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509180</v>
+        <v>509124</v>
       </c>
       <c r="R13" t="n">
-        <v>6716322</v>
+        <v>6716239</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1940,32 +1922,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132344674</v>
+        <v>132359393</v>
       </c>
       <c r="B14" t="n">
-        <v>92639</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1978,13 +1960,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509198</v>
+        <v>509156</v>
       </c>
       <c r="R14" t="n">
-        <v>6716199</v>
+        <v>6716223</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,22 +2011,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132344681</v>
+        <v>132359418</v>
       </c>
       <c r="B15" t="n">
-        <v>91936</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,19 +2034,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -2075,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509233</v>
+        <v>509155</v>
       </c>
       <c r="R15" t="n">
-        <v>6716365</v>
+        <v>6716231</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,22 +2112,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132359137</v>
+        <v>132359657</v>
       </c>
       <c r="B16" t="n">
-        <v>91916</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509088</v>
+        <v>509226</v>
       </c>
       <c r="R16" t="n">
-        <v>6716080</v>
+        <v>6716352</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2239,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132359184</v>
+        <v>132344676</v>
       </c>
       <c r="B17" t="n">
-        <v>91916</v>
+        <v>92406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,13 +2263,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509103</v>
+        <v>509232</v>
       </c>
       <c r="R17" t="n">
-        <v>6716073</v>
+        <v>6716372</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2328,44 +2314,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132359418</v>
+        <v>132344674</v>
       </c>
       <c r="B18" t="n">
-        <v>91916</v>
+        <v>92199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2378,13 +2364,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509155</v>
+        <v>509198</v>
       </c>
       <c r="R18" t="n">
-        <v>6716231</v>
+        <v>6716199</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,44 +2415,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132359393</v>
+        <v>132344675</v>
       </c>
       <c r="B19" t="n">
-        <v>91916</v>
+        <v>92199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,13 +2465,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509156</v>
+        <v>509242</v>
       </c>
       <c r="R19" t="n">
-        <v>6716223</v>
+        <v>6716353</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2530,22 +2516,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132359259</v>
+        <v>132359052</v>
       </c>
       <c r="B20" t="n">
-        <v>92215</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,26 +2539,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2580,13 +2571,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509095</v>
+        <v>509089</v>
       </c>
       <c r="R20" t="n">
-        <v>6716085</v>
+        <v>6716171</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,13 +2609,17 @@
           <t>2026-04-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2643,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132359149</v>
+        <v>132359089</v>
       </c>
       <c r="B21" t="n">
-        <v>91916</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,26 +2649,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509082</v>
+        <v>509102</v>
       </c>
       <c r="R21" t="n">
-        <v>6716062</v>
+        <v>6716083</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2719,13 +2719,17 @@
           <t>2026-04-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2741,107 +2745,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>132359333</v>
-      </c>
-      <c r="B22" t="n">
-        <v>91916</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Slomtjärnsbäcken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>509124</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6716239</v>
-      </c>
-      <c r="S22" t="n">
-        <v>25</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Gagnef</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Gagnef</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11259-2026 artfynd.xlsx
+++ b/artfynd/A 11259-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359259</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359304</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359353</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359450</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359137</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359149</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359184</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359213</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359333</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359393</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359418</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2222,6 +2297,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359657</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2323,6 +2403,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344676</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2424,6 +2509,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344674</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2525,6 +2615,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344675</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359052</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2745,8 +2845,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132359089</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>